--- a/output/Data and Chart Outputs/peru_gas_demand_by_sector.xlsx
+++ b/output/Data and Chart Outputs/peru_gas_demand_by_sector.xlsx
@@ -355,7 +355,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Peru gas production by lot vs domestic demand and LNG exports (to Aug/26)</a:t>
+              <a:t>Peru gas supply vs demand + LNG (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>LNG exports</t>
+          <t>Domestic demand + LNG exports</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
         <v>14.4359</v>
       </c>
       <c r="H2" t="n">
-        <v>12.59</v>
+        <v>27.0259</v>
       </c>
     </row>
     <row r="3">
@@ -2486,7 +2486,7 @@
         <v>14.0488</v>
       </c>
       <c r="H3" t="n">
-        <v>13.7119</v>
+        <v>27.7607</v>
       </c>
     </row>
     <row r="4">
@@ -2512,7 +2512,7 @@
         <v>15.199</v>
       </c>
       <c r="H4" t="n">
-        <v>15.2042</v>
+        <v>30.4032</v>
       </c>
     </row>
     <row r="5">
@@ -2538,7 +2538,7 @@
         <v>13.7395</v>
       </c>
       <c r="H5" t="n">
-        <v>9.4778</v>
+        <v>23.2173</v>
       </c>
     </row>
     <row r="6">
@@ -2564,7 +2564,7 @@
         <v>18.2978</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>18.2978</v>
       </c>
     </row>
     <row r="7">
@@ -2590,7 +2590,7 @@
         <v>20.8835</v>
       </c>
       <c r="H7" t="n">
-        <v>8.370900000000001</v>
+        <v>29.2544</v>
       </c>
     </row>
     <row r="8">
@@ -2616,7 +2616,7 @@
         <v>20.7654</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>20.7654</v>
       </c>
     </row>
     <row r="9">
@@ -2642,7 +2642,7 @@
         <v>22.398</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>22.398</v>
       </c>
     </row>
     <row r="10">
@@ -2668,7 +2668,7 @@
         <v>22.844</v>
       </c>
       <c r="H10" t="n">
-        <v>9.332700000000001</v>
+        <v>32.1767</v>
       </c>
     </row>
     <row r="11">
@@ -2694,7 +2694,7 @@
         <v>20.024</v>
       </c>
       <c r="H11" t="n">
-        <v>13.2418</v>
+        <v>33.2658</v>
       </c>
     </row>
     <row r="12">
@@ -2720,7 +2720,7 @@
         <v>19.8549</v>
       </c>
       <c r="H12" t="n">
-        <v>16.4027</v>
+        <v>36.2576</v>
       </c>
     </row>
     <row r="13">
@@ -2746,7 +2746,7 @@
         <v>17.759</v>
       </c>
       <c r="H13" t="n">
-        <v>18.1463</v>
+        <v>35.9053</v>
       </c>
     </row>
     <row r="14">
@@ -2772,7 +2772,7 @@
         <v>17.0959</v>
       </c>
       <c r="H14" t="n">
-        <v>18.7707</v>
+        <v>35.86660000000001</v>
       </c>
     </row>
     <row r="15">
@@ -2798,7 +2798,7 @@
         <v>16.8388</v>
       </c>
       <c r="H15" t="n">
-        <v>16.2558</v>
+        <v>33.0946</v>
       </c>
     </row>
     <row r="16">
@@ -2824,7 +2824,7 @@
         <v>16.4733</v>
       </c>
       <c r="H16" t="n">
-        <v>15.2157</v>
+        <v>31.689</v>
       </c>
     </row>
     <row r="17">
@@ -2850,7 +2850,7 @@
         <v>15.2581</v>
       </c>
       <c r="H17" t="n">
-        <v>19.941</v>
+        <v>35.1991</v>
       </c>
     </row>
     <row r="18">
@@ -2876,7 +2876,7 @@
         <v>18.9006</v>
       </c>
       <c r="H18" t="n">
-        <v>16.0609</v>
+        <v>34.9615</v>
       </c>
     </row>
     <row r="19">
@@ -2902,7 +2902,7 @@
         <v>21.4286</v>
       </c>
       <c r="H19" t="n">
-        <v>15.2675</v>
+        <v>36.6961</v>
       </c>
     </row>
     <row r="20">
@@ -2928,7 +2928,7 @@
         <v>21.9114</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>21.9114</v>
       </c>
     </row>
     <row r="21">
@@ -2954,7 +2954,7 @@
         <v>22.5687</v>
       </c>
       <c r="H21" t="n">
-        <v>7.7185</v>
+        <v>30.2872</v>
       </c>
     </row>
     <row r="22">
@@ -2980,7 +2980,7 @@
         <v>23.1991</v>
       </c>
       <c r="H22" t="n">
-        <v>5.5996</v>
+        <v>28.7987</v>
       </c>
     </row>
     <row r="23">
@@ -3006,7 +3006,7 @@
         <v>23.0667</v>
       </c>
       <c r="H23" t="n">
-        <v>15.2128</v>
+        <v>38.2795</v>
       </c>
     </row>
     <row r="24">
@@ -3032,7 +3032,7 @@
         <v>25.0294</v>
       </c>
       <c r="H24" t="n">
-        <v>13.9374</v>
+        <v>38.9668</v>
       </c>
     </row>
     <row r="25">
@@ -3058,7 +3058,7 @@
         <v>23.1523</v>
       </c>
       <c r="H25" t="n">
-        <v>12.7112</v>
+        <v>35.8635</v>
       </c>
     </row>
     <row r="26">
@@ -3084,7 +3084,7 @@
         <v>19.4907</v>
       </c>
       <c r="H26" t="n">
-        <v>15.6703</v>
+        <v>35.161</v>
       </c>
     </row>
     <row r="27">
@@ -3110,7 +3110,7 @@
         <v>18.3147</v>
       </c>
       <c r="H27" t="n">
-        <v>17.7332</v>
+        <v>36.0479</v>
       </c>
     </row>
     <row r="28">
@@ -3136,7 +3136,7 @@
         <v>20.5563</v>
       </c>
       <c r="H28" t="n">
-        <v>15.9596</v>
+        <v>36.5159</v>
       </c>
     </row>
     <row r="29">
@@ -3162,7 +3162,7 @@
         <v>18.2702</v>
       </c>
       <c r="H29" t="n">
-        <v>18.2212</v>
+        <v>36.4914</v>
       </c>
     </row>
     <row r="30">
@@ -3188,7 +3188,7 @@
         <v>21.4922</v>
       </c>
       <c r="H30" t="n">
-        <v>12.0574</v>
+        <v>33.5496</v>
       </c>
     </row>
     <row r="31">
@@ -3214,7 +3214,7 @@
         <v>24.3537</v>
       </c>
       <c r="H31" t="n">
-        <v>15.914</v>
+        <v>40.2677</v>
       </c>
     </row>
     <row r="32">
@@ -3240,7 +3240,7 @@
         <v>22.5539</v>
       </c>
       <c r="H32" t="n">
-        <v>9.892300000000001</v>
+        <v>32.4462</v>
       </c>
     </row>
     <row r="33">
@@ -3266,7 +3266,7 @@
         <v>24.0461</v>
       </c>
       <c r="H33" t="n">
-        <v>4.3844</v>
+        <v>28.4305</v>
       </c>
     </row>
     <row r="34">
@@ -3292,7 +3292,7 @@
         <v>25.3516</v>
       </c>
       <c r="H34" t="n">
-        <v>16.9002</v>
+        <v>42.2518</v>
       </c>
     </row>
     <row r="35">
@@ -3318,7 +3318,7 @@
         <v>23.3626</v>
       </c>
       <c r="H35" t="n">
-        <v>11.144</v>
+        <v>34.5066</v>
       </c>
     </row>
     <row r="36">
@@ -3344,7 +3344,7 @@
         <v>22.4217</v>
       </c>
       <c r="H36" t="n">
-        <v>12.4097</v>
+        <v>34.8314</v>
       </c>
     </row>
     <row r="37">
@@ -3370,7 +3370,7 @@
         <v>17.7357</v>
       </c>
       <c r="H37" t="n">
-        <v>16.3831</v>
+        <v>34.1188</v>
       </c>
     </row>
     <row r="38">
@@ -3396,7 +3396,7 @@
         <v>17.5465</v>
       </c>
       <c r="H38" t="n">
-        <v>16.0112</v>
+        <v>33.5577</v>
       </c>
     </row>
     <row r="39">
@@ -3422,7 +3422,7 @@
         <v>18.7692</v>
       </c>
       <c r="H39" t="n">
-        <v>14.2057</v>
+        <v>32.97490000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3448,7 +3448,7 @@
         <v>18.2451</v>
       </c>
       <c r="H40" t="n">
-        <v>15.5399</v>
+        <v>33.785</v>
       </c>
     </row>
     <row r="41">
@@ -3474,7 +3474,7 @@
         <v>17.4447</v>
       </c>
       <c r="H41" t="n">
-        <v>17.0021</v>
+        <v>34.4468</v>
       </c>
     </row>
     <row r="42">
@@ -3500,7 +3500,7 @@
         <v>20.1486</v>
       </c>
       <c r="H42" t="n">
-        <v>15.5421</v>
+        <v>35.6907</v>
       </c>
     </row>
     <row r="43">
@@ -3526,7 +3526,7 @@
         <v>22.8507</v>
       </c>
       <c r="H43" t="n">
-        <v>13.3398</v>
+        <v>36.1905</v>
       </c>
     </row>
     <row r="44">
@@ -3552,7 +3552,7 @@
         <v>23.8869</v>
       </c>
       <c r="H44" t="n">
-        <v>10.9639</v>
+        <v>34.8508</v>
       </c>
     </row>
     <row r="45">
@@ -3578,7 +3578,7 @@
         <v>23.7012</v>
       </c>
       <c r="H45" t="n">
-        <v>11.6094</v>
+        <v>35.3106</v>
       </c>
     </row>
     <row r="46">
@@ -3604,7 +3604,7 @@
         <v>23.8299</v>
       </c>
       <c r="H46" t="n">
-        <v>19.6032</v>
+        <v>43.4331</v>
       </c>
     </row>
     <row r="47">
@@ -3630,7 +3630,7 @@
         <v>23.5471</v>
       </c>
       <c r="H47" t="n">
-        <v>8.985200000000001</v>
+        <v>32.5323</v>
       </c>
     </row>
     <row r="48">
@@ -3656,7 +3656,7 @@
         <v>22.2448</v>
       </c>
       <c r="H48" t="n">
-        <v>17.0151</v>
+        <v>39.2599</v>
       </c>
     </row>
     <row r="49">
@@ -3682,7 +3682,7 @@
         <v>17.1663</v>
       </c>
       <c r="H49" t="n">
-        <v>18.7061</v>
+        <v>35.8724</v>
       </c>
     </row>
     <row r="50">
@@ -3708,7 +3708,7 @@
         <v>16.7342</v>
       </c>
       <c r="H50" t="n">
-        <v>10.0017</v>
+        <v>26.7359</v>
       </c>
     </row>
     <row r="51">
@@ -3734,7 +3734,7 @@
         <v>19.8182</v>
       </c>
       <c r="H51" t="n">
-        <v>14.4987</v>
+        <v>34.3169</v>
       </c>
     </row>
     <row r="52">
@@ -3760,7 +3760,7 @@
         <v>19.844</v>
       </c>
       <c r="H52" t="n">
-        <v>16.4905</v>
+        <v>36.33450000000001</v>
       </c>
     </row>
     <row r="53">
@@ -3786,7 +3786,7 @@
         <v>17.5735</v>
       </c>
       <c r="H53" t="n">
-        <v>8.174300000000001</v>
+        <v>25.7478</v>
       </c>
     </row>
     <row r="54">
@@ -3812,7 +3812,7 @@
         <v>19.269</v>
       </c>
       <c r="H54" t="n">
-        <v>16.489</v>
+        <v>35.758</v>
       </c>
     </row>
     <row r="55">
@@ -3838,7 +3838,7 @@
         <v>21.2137</v>
       </c>
       <c r="H55" t="n">
-        <v>13.1708</v>
+        <v>34.3845</v>
       </c>
     </row>
     <row r="56">
@@ -3864,7 +3864,7 @@
         <v>23.1381</v>
       </c>
       <c r="H56" t="n">
-        <v>15.4112</v>
+        <v>38.5493</v>
       </c>
     </row>
     <row r="57">
@@ -3890,7 +3890,7 @@
         <v>23.3768</v>
       </c>
       <c r="H57" t="n">
-        <v>11.9145</v>
+        <v>35.2913</v>
       </c>
     </row>
     <row r="58">
@@ -3916,7 +3916,7 @@
         <v>23.9396</v>
       </c>
       <c r="H58" t="n">
-        <v>16.5515</v>
+        <v>40.4911</v>
       </c>
     </row>
     <row r="59">
@@ -3942,7 +3942,7 @@
         <v>20.5018</v>
       </c>
       <c r="H59" t="n">
-        <v>13.2661</v>
+        <v>33.7679</v>
       </c>
     </row>
     <row r="60">
@@ -3968,7 +3968,7 @@
         <v>20.6515</v>
       </c>
       <c r="H60" t="n">
-        <v>13.948</v>
+        <v>34.5995</v>
       </c>
     </row>
     <row r="61">
@@ -3994,7 +3994,7 @@
         <v>23.2175</v>
       </c>
       <c r="H61" t="n">
-        <v>13.2549</v>
+        <v>36.4724</v>
       </c>
     </row>
     <row r="62">
@@ -4020,7 +4020,7 @@
         <v>20.1413</v>
       </c>
       <c r="H62" t="n">
-        <v>13.3256</v>
+        <v>33.4669</v>
       </c>
     </row>
     <row r="63">
@@ -4046,7 +4046,7 @@
         <v>19.6902</v>
       </c>
       <c r="H63" t="n">
-        <v>14.352</v>
+        <v>34.0422</v>
       </c>
     </row>
     <row r="64">
@@ -4072,7 +4072,7 @@
         <v>13.7152</v>
       </c>
       <c r="H64" t="n">
-        <v>5.9391</v>
+        <v>19.6543</v>
       </c>
     </row>
     <row r="65">
@@ -4098,7 +4098,7 @@
         <v>19.6987</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>19.6987</v>
       </c>
     </row>
     <row r="66">
@@ -4124,7 +4124,7 @@
         <v>21.1446</v>
       </c>
       <c r="H66" t="n">
-        <v>15.7192</v>
+        <v>36.8638</v>
       </c>
     </row>
     <row r="67">
@@ -4150,7 +4150,7 @@
         <v>23.6515</v>
       </c>
       <c r="H67" t="n">
-        <v>16.1458</v>
+        <v>39.7973</v>
       </c>
     </row>
     <row r="68">
@@ -4176,7 +4176,7 @@
         <v>24.8729</v>
       </c>
       <c r="H68" t="n">
-        <v>15.5437</v>
+        <v>40.4166</v>
       </c>
     </row>
     <row r="69">
@@ -4202,7 +4202,7 @@
         <v>27.4387</v>
       </c>
       <c r="H69" t="n">
-        <v>15.761</v>
+        <v>43.1997</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/peru_gas_demand_by_sector.xlsx
+++ b/output/Data and Chart Outputs/peru_gas_demand_by_sector.xlsx
@@ -24,8 +24,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -65,9 +66,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -162,6 +164,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -290,11 +293,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -322,14 +337,22 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -360,6 +383,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -593,11 +617,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -625,14 +661,22 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1124,7 +1168,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Demand monthly 2021-01..2026-08; production 2021-01..2026-08; LNG cargoes 2021-01..2026-09; daily power estimate 2021-01-01..2026-09-29. MINEM publishes about four weeks after month end. Demand Jan-2022 on from the monthly distribution files (the last 6 months are re-read each run); 2021 from the Anuario Estadistico de Hidrocarburos 2021 tables (fetched once).</t>
+          <t>Demand monthly 2021-01..2026-08; production 2021-01..2026-08; LNG cargoes 2021-01..2026-09; daily power estimate 2021-01-01..2026-09-30. MINEM publishes about four weeks after month end. Demand Jan-2022 on from the monthly distribution files (the last 6 months are re-read each run); 2021 from the Anuario Estadistico de Hidrocarburos 2021 tables (fetched once).</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1266,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1239,7 +1283,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1256,7 +1300,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1273,7 +1317,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1290,7 +1334,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1307,7 +1351,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1324,7 +1368,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1341,7 +1385,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1358,7 +1402,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1375,7 +1419,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1392,7 +1436,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1409,7 +1453,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1426,7 +1470,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1443,7 +1487,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1460,7 +1504,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1477,7 +1521,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1494,7 +1538,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1511,7 +1555,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1528,7 +1572,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1545,7 +1589,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1562,7 +1606,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1579,7 +1623,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1596,7 +1640,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1613,7 +1657,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1630,7 +1674,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1647,7 +1691,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1664,7 +1708,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1681,7 +1725,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1698,7 +1742,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1715,7 +1759,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1732,7 +1776,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1749,7 +1793,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1766,7 +1810,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1783,7 +1827,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1800,7 +1844,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1817,7 +1861,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1834,7 +1878,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -1851,7 +1895,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -1868,7 +1912,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -1885,7 +1929,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -1902,7 +1946,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -1919,7 +1963,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -1936,7 +1980,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -1953,7 +1997,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -1970,7 +2014,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -1987,7 +2031,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2004,7 +2048,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2021,7 +2065,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2038,7 +2082,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2055,7 +2099,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2072,7 +2116,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2089,7 +2133,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2106,7 +2150,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2123,7 +2167,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2140,7 +2184,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2157,7 +2201,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2174,7 +2218,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2191,7 +2235,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2208,7 +2252,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2225,7 +2269,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2242,7 +2286,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2259,7 +2303,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2276,7 +2320,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2293,7 +2337,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2310,7 +2354,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2327,7 +2371,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2344,7 +2388,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2361,7 +2405,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -2438,7 +2482,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -2464,7 +2508,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -2490,7 +2534,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -2516,7 +2560,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -2542,7 +2586,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -2568,7 +2612,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -2594,7 +2638,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -2620,7 +2664,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -2646,7 +2690,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -2672,7 +2716,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -2698,7 +2742,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -2724,7 +2768,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -2750,7 +2794,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -2776,7 +2820,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -2802,7 +2846,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -2828,7 +2872,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -2854,7 +2898,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -2880,7 +2924,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -2906,7 +2950,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -2932,7 +2976,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -2958,7 +3002,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -2984,7 +3028,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -3010,7 +3054,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -3036,7 +3080,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -3062,7 +3106,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -3088,7 +3132,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -3114,7 +3158,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -3140,7 +3184,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -3166,7 +3210,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -3192,7 +3236,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -3218,7 +3262,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -3244,7 +3288,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -3270,7 +3314,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -3296,7 +3340,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -3322,7 +3366,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -3348,7 +3392,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -3374,7 +3418,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -3400,7 +3444,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -3426,7 +3470,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -3452,7 +3496,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -3478,7 +3522,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -3504,7 +3548,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -3530,7 +3574,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -3556,7 +3600,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -3582,7 +3626,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -3608,7 +3652,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -3634,7 +3678,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -3660,7 +3704,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -3686,7 +3730,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -3712,7 +3756,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -3738,7 +3782,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -3764,7 +3808,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -3790,7 +3834,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -3816,7 +3860,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -3842,7 +3886,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -3868,7 +3912,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -3894,7 +3938,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -3920,7 +3964,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -3946,7 +3990,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -3972,7 +4016,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -3998,7 +4042,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -4024,7 +4068,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -4050,7 +4094,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -4076,7 +4120,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -4102,7 +4146,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -4128,7 +4172,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -4154,7 +4198,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -4180,7 +4224,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -12613,13 +12657,13 @@
         <v>15488592</v>
       </c>
       <c r="F70" t="n">
-        <v>14504.3</v>
+        <v>14504.5</v>
       </c>
       <c r="G70" t="n">
-        <v>483.478</v>
+        <v>483.482</v>
       </c>
       <c r="H70" t="n">
-        <v>13.6906</v>
+        <v>13.6907</v>
       </c>
     </row>
   </sheetData>
@@ -13757,7 +13801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2099"/>
+  <dimension ref="A1:F2100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64142,6 +64186,30 @@
       </c>
       <c r="F2099" t="n">
         <v>18.1933</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2100" t="n">
+        <v>88516.39999999999</v>
+      </c>
+      <c r="C2100" t="n">
+        <v>7468</v>
+      </c>
+      <c r="D2100" t="inlineStr">
+        <is>
+          <t>trailing 12-month mean</t>
+        </is>
+      </c>
+      <c r="E2100" t="n">
+        <v>620.705</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>17.5764</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/peru_gas_demand_by_sector.xlsx
+++ b/output/Data and Chart Outputs/peru_gas_demand_by_sector.xlsx
@@ -159,7 +159,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Peru gas demand by sector (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Peru gas demand by sector (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -189,12 +190,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$69</f>
+              <f>'Chart'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -217,12 +218,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$69</f>
+              <f>'Chart'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -245,12 +246,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$69</f>
+              <f>'Chart'!$D$2:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -273,12 +274,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$69</f>
+              <f>'Chart'!$E$2:$E$70</f>
             </numRef>
           </val>
         </ser>
@@ -378,6 +379,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Peru gas supply vs demand + LNG (to Aug/26)</a:t>
             </a:r>
           </a:p>
@@ -1168,7 +1170,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Demand monthly 2021-01..2026-08; production 2021-01..2026-08; LNG cargoes 2021-01..2026-09; daily power estimate 2021-01-01..2026-09-30. MINEM publishes about four weeks after month end. Demand Jan-2022 on from the monthly distribution files (the last 6 months are re-read each run); 2021 from the Anuario Estadistico de Hidrocarburos 2021 tables (fetched once).</t>
+          <t>Demand monthly 2021-01..2026-09; production 2021-01..2026-08; LNG cargoes 2021-01..2026-09; daily power estimate 2021-01-01..2026-10-01. MINEM publishes about four weeks after month end. Demand Jan-2022 on from the monthly distribution files (the last 6 months are re-read each run); 2021 from the Anuario Estadistico de Hidrocarburos 2021 tables (fetched once).</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1191,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Latest distribution file: https://cdn.www.gob.pe/uploads/document/file/10615630/8592727-distribucion-agosto-2026.xlsx</t>
+          <t>Latest distribution file: https://cdn.www.gob.pe/uploads/document/file/10785810/8714379-distribucion-setiembre-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2409,16 +2411,33 @@
         <v>46235</v>
       </c>
       <c r="B69" t="n">
-        <v>17.815</v>
+        <v>15.1739</v>
       </c>
       <c r="C69" t="n">
-        <v>5.6227</v>
+        <v>5.6491</v>
       </c>
       <c r="D69" t="n">
-        <v>2.7123</v>
+        <v>2.5474</v>
       </c>
       <c r="E69" t="n">
-        <v>1.2888</v>
+        <v>1.2152</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>17.2199</v>
+      </c>
+      <c r="C70" t="n">
+        <v>6.1647</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2.8901</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1.3702</v>
       </c>
     </row>
   </sheetData>
@@ -4243,10 +4262,10 @@
         <v>1.8399</v>
       </c>
       <c r="G69" t="n">
-        <v>27.4387</v>
+        <v>24.5856</v>
       </c>
       <c r="H69" t="n">
-        <v>43.1997</v>
+        <v>40.3466</v>
       </c>
     </row>
   </sheetData>
@@ -4261,7 +4280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6807,34 +6826,71 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>17.815</v>
+        <v>15.1739</v>
       </c>
       <c r="C69" t="n">
-        <v>5.6227</v>
+        <v>5.6491</v>
       </c>
       <c r="D69" t="n">
-        <v>2.7123</v>
+        <v>2.5474</v>
       </c>
       <c r="E69" t="n">
-        <v>1.2888</v>
+        <v>1.2152</v>
       </c>
       <c r="F69" t="n">
-        <v>27.4387</v>
+        <v>24.5856</v>
       </c>
       <c r="G69" t="n">
-        <v>629.129</v>
+        <v>535.8630000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>198.562</v>
+        <v>199.498</v>
       </c>
       <c r="I69" t="n">
-        <v>95.783</v>
+        <v>89.959</v>
       </c>
       <c r="J69" t="n">
-        <v>45.512</v>
+        <v>42.913</v>
       </c>
       <c r="K69" t="n">
-        <v>968.987</v>
+        <v>868.2329999999999</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>17.2199</v>
+      </c>
+      <c r="C70" t="n">
+        <v>6.1647</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2.8901</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1.3702</v>
+      </c>
+      <c r="F70" t="n">
+        <v>27.6449</v>
+      </c>
+      <c r="G70" t="n">
+        <v>608.115</v>
+      </c>
+      <c r="H70" t="n">
+        <v>217.704</v>
+      </c>
+      <c r="I70" t="n">
+        <v>102.064</v>
+      </c>
+      <c r="J70" t="n">
+        <v>48.389</v>
+      </c>
+      <c r="K70" t="n">
+        <v>976.271</v>
       </c>
     </row>
   </sheetData>
@@ -10672,10 +10728,10 @@
         <v>1639.075</v>
       </c>
       <c r="P69" t="n">
-        <v>968.987</v>
+        <v>868.2329999999999</v>
       </c>
       <c r="Q69" t="n">
-        <v>670.088</v>
+        <v>770.842</v>
       </c>
     </row>
   </sheetData>
@@ -12645,7 +12701,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C70" t="n">
         <v>667757.3</v>
@@ -12677,7 +12733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13781,13 +13837,29 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>629.129</v>
+        <v>535.8630000000001</v>
       </c>
       <c r="C69" t="n">
         <v>85.004</v>
       </c>
       <c r="D69" t="n">
-        <v>7882.209</v>
+        <v>6713.693</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>608.115</v>
+      </c>
+      <c r="C70" t="n">
+        <v>87.81999999999999</v>
+      </c>
+      <c r="D70" t="n">
+        <v>7374.619</v>
       </c>
     </row>
   </sheetData>
@@ -13801,7 +13873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2100"/>
+  <dimension ref="A1:F2101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62758,7 +62830,7 @@
         <v>84794.3</v>
       </c>
       <c r="C2040" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2040" t="inlineStr">
         <is>
@@ -62766,10 +62838,10 @@
         </is>
       </c>
       <c r="E2040" t="n">
-        <v>627.574</v>
+        <v>534.538</v>
       </c>
       <c r="F2040" t="n">
-        <v>17.7709</v>
+        <v>15.1364</v>
       </c>
     </row>
     <row r="2041">
@@ -62782,7 +62854,7 @@
         <v>73478.2</v>
       </c>
       <c r="C2041" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2041" t="inlineStr">
         <is>
@@ -62790,10 +62862,10 @@
         </is>
       </c>
       <c r="E2041" t="n">
-        <v>543.822</v>
+        <v>463.202</v>
       </c>
       <c r="F2041" t="n">
-        <v>15.3993</v>
+        <v>13.1164</v>
       </c>
     </row>
     <row r="2042">
@@ -62806,7 +62878,7 @@
         <v>84445.39999999999</v>
       </c>
       <c r="C2042" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2042" t="inlineStr">
         <is>
@@ -62814,10 +62886,10 @@
         </is>
       </c>
       <c r="E2042" t="n">
-        <v>624.992</v>
+        <v>532.338</v>
       </c>
       <c r="F2042" t="n">
-        <v>17.6978</v>
+        <v>15.0741</v>
       </c>
     </row>
     <row r="2043">
@@ -62830,7 +62902,7 @@
         <v>87898.89999999999</v>
       </c>
       <c r="C2043" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2043" t="inlineStr">
         <is>
@@ -62838,10 +62910,10 @@
         </is>
       </c>
       <c r="E2043" t="n">
-        <v>650.552</v>
+        <v>554.109</v>
       </c>
       <c r="F2043" t="n">
-        <v>18.4216</v>
+        <v>15.6906</v>
       </c>
     </row>
     <row r="2044">
@@ -62854,7 +62926,7 @@
         <v>86237.39999999999</v>
       </c>
       <c r="C2044" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2044" t="inlineStr">
         <is>
@@ -62862,10 +62934,10 @@
         </is>
       </c>
       <c r="E2044" t="n">
-        <v>638.255</v>
+        <v>543.635</v>
       </c>
       <c r="F2044" t="n">
-        <v>18.0734</v>
+        <v>15.394</v>
       </c>
     </row>
     <row r="2045">
@@ -62878,7 +62950,7 @@
         <v>87068.10000000001</v>
       </c>
       <c r="C2045" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2045" t="inlineStr">
         <is>
@@ -62886,10 +62958,10 @@
         </is>
       </c>
       <c r="E2045" t="n">
-        <v>644.403</v>
+        <v>548.872</v>
       </c>
       <c r="F2045" t="n">
-        <v>18.2475</v>
+        <v>15.5423</v>
       </c>
     </row>
     <row r="2046">
@@ -62902,7 +62974,7 @@
         <v>89072.7</v>
       </c>
       <c r="C2046" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2046" t="inlineStr">
         <is>
@@ -62910,10 +62982,10 @@
         </is>
       </c>
       <c r="E2046" t="n">
-        <v>659.239</v>
+        <v>561.509</v>
       </c>
       <c r="F2046" t="n">
-        <v>18.6676</v>
+        <v>15.9002</v>
       </c>
     </row>
     <row r="2047">
@@ -62926,7 +62998,7 @@
         <v>85989.2</v>
       </c>
       <c r="C2047" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2047" t="inlineStr">
         <is>
@@ -62934,10 +63006,10 @@
         </is>
       </c>
       <c r="E2047" t="n">
-        <v>636.418</v>
+        <v>542.071</v>
       </c>
       <c r="F2047" t="n">
-        <v>18.0214</v>
+        <v>15.3497</v>
       </c>
     </row>
     <row r="2048">
@@ -62950,7 +63022,7 @@
         <v>80557.39999999999</v>
       </c>
       <c r="C2048" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2048" t="inlineStr">
         <is>
@@ -62958,10 +63030,10 @@
         </is>
       </c>
       <c r="E2048" t="n">
-        <v>596.216</v>
+        <v>507.829</v>
       </c>
       <c r="F2048" t="n">
-        <v>16.883</v>
+        <v>14.3801</v>
       </c>
     </row>
     <row r="2049">
@@ -62974,7 +63046,7 @@
         <v>85474.60000000001</v>
       </c>
       <c r="C2049" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2049" t="inlineStr">
         <is>
@@ -62982,10 +63054,10 @@
         </is>
       </c>
       <c r="E2049" t="n">
-        <v>632.609</v>
+        <v>538.827</v>
       </c>
       <c r="F2049" t="n">
-        <v>17.9135</v>
+        <v>15.2579</v>
       </c>
     </row>
     <row r="2050">
@@ -62998,7 +63070,7 @@
         <v>84117.5</v>
       </c>
       <c r="C2050" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2050" t="inlineStr">
         <is>
@@ -63006,10 +63078,10 @@
         </is>
       </c>
       <c r="E2050" t="n">
-        <v>622.5650000000001</v>
+        <v>530.271</v>
       </c>
       <c r="F2050" t="n">
-        <v>17.6291</v>
+        <v>15.0156</v>
       </c>
     </row>
     <row r="2051">
@@ -63022,7 +63094,7 @@
         <v>86262.10000000001</v>
       </c>
       <c r="C2051" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2051" t="inlineStr">
         <is>
@@ -63030,10 +63102,10 @@
         </is>
       </c>
       <c r="E2051" t="n">
-        <v>638.437</v>
+        <v>543.7910000000001</v>
       </c>
       <c r="F2051" t="n">
-        <v>18.0785</v>
+        <v>15.3984</v>
       </c>
     </row>
     <row r="2052">
@@ -63046,7 +63118,7 @@
         <v>86453.8</v>
       </c>
       <c r="C2052" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2052" t="inlineStr">
         <is>
@@ -63054,10 +63126,10 @@
         </is>
       </c>
       <c r="E2052" t="n">
-        <v>639.856</v>
+        <v>544.999</v>
       </c>
       <c r="F2052" t="n">
-        <v>18.1187</v>
+        <v>15.4327</v>
       </c>
     </row>
     <row r="2053">
@@ -63070,7 +63142,7 @@
         <v>84405.5</v>
       </c>
       <c r="C2053" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2053" t="inlineStr">
         <is>
@@ -63078,10 +63150,10 @@
         </is>
       </c>
       <c r="E2053" t="n">
-        <v>624.696</v>
+        <v>532.087</v>
       </c>
       <c r="F2053" t="n">
-        <v>17.6894</v>
+        <v>15.067</v>
       </c>
     </row>
     <row r="2054">
@@ -63094,7 +63166,7 @@
         <v>88448</v>
       </c>
       <c r="C2054" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2054" t="inlineStr">
         <is>
@@ -63102,10 +63174,10 @@
         </is>
       </c>
       <c r="E2054" t="n">
-        <v>654.616</v>
+        <v>557.571</v>
       </c>
       <c r="F2054" t="n">
-        <v>18.5367</v>
+        <v>15.7887</v>
       </c>
     </row>
     <row r="2055">
@@ -63118,7 +63190,7 @@
         <v>84479.7</v>
       </c>
       <c r="C2055" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2055" t="inlineStr">
         <is>
@@ -63126,10 +63198,10 @@
         </is>
       </c>
       <c r="E2055" t="n">
-        <v>625.246</v>
+        <v>532.5549999999999</v>
       </c>
       <c r="F2055" t="n">
-        <v>17.705</v>
+        <v>15.0803</v>
       </c>
     </row>
     <row r="2056">
@@ -63142,7 +63214,7 @@
         <v>89361.2</v>
       </c>
       <c r="C2056" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2056" t="inlineStr">
         <is>
@@ -63150,10 +63222,10 @@
         </is>
       </c>
       <c r="E2056" t="n">
-        <v>661.374</v>
+        <v>563.327</v>
       </c>
       <c r="F2056" t="n">
-        <v>18.728</v>
+        <v>15.9516</v>
       </c>
     </row>
     <row r="2057">
@@ -63166,7 +63238,7 @@
         <v>80061.5</v>
       </c>
       <c r="C2057" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2057" t="inlineStr">
         <is>
@@ -63174,10 +63246,10 @@
         </is>
       </c>
       <c r="E2057" t="n">
-        <v>592.546</v>
+        <v>504.703</v>
       </c>
       <c r="F2057" t="n">
-        <v>16.779</v>
+        <v>14.2916</v>
       </c>
     </row>
     <row r="2058">
@@ -63190,7 +63262,7 @@
         <v>71010.2</v>
       </c>
       <c r="C2058" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2058" t="inlineStr">
         <is>
@@ -63198,10 +63270,10 @@
         </is>
       </c>
       <c r="E2058" t="n">
-        <v>525.556</v>
+        <v>447.644</v>
       </c>
       <c r="F2058" t="n">
-        <v>14.8821</v>
+        <v>12.6759</v>
       </c>
     </row>
     <row r="2059">
@@ -63214,7 +63286,7 @@
         <v>77636.89999999999</v>
       </c>
       <c r="C2059" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2059" t="inlineStr">
         <is>
@@ -63222,10 +63294,10 @@
         </is>
       </c>
       <c r="E2059" t="n">
-        <v>574.601</v>
+        <v>489.418</v>
       </c>
       <c r="F2059" t="n">
-        <v>16.2709</v>
+        <v>13.8588</v>
       </c>
     </row>
     <row r="2060">
@@ -63238,7 +63310,7 @@
         <v>87475</v>
       </c>
       <c r="C2060" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2060" t="inlineStr">
         <is>
@@ -63246,10 +63318,10 @@
         </is>
       </c>
       <c r="E2060" t="n">
-        <v>647.414</v>
+        <v>551.437</v>
       </c>
       <c r="F2060" t="n">
-        <v>18.3327</v>
+        <v>15.615</v>
       </c>
     </row>
     <row r="2061">
@@ -63262,7 +63334,7 @@
         <v>88731.2</v>
       </c>
       <c r="C2061" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2061" t="inlineStr">
         <is>
@@ -63270,10 +63342,10 @@
         </is>
       </c>
       <c r="E2061" t="n">
-        <v>656.712</v>
+        <v>559.356</v>
       </c>
       <c r="F2061" t="n">
-        <v>18.596</v>
+        <v>15.8392</v>
       </c>
     </row>
     <row r="2062">
@@ -63286,7 +63358,7 @@
         <v>86679.10000000001</v>
       </c>
       <c r="C2062" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2062" t="inlineStr">
         <is>
@@ -63294,10 +63366,10 @@
         </is>
       </c>
       <c r="E2062" t="n">
-        <v>641.524</v>
+        <v>546.42</v>
       </c>
       <c r="F2062" t="n">
-        <v>18.1659</v>
+        <v>15.4729</v>
       </c>
     </row>
     <row r="2063">
@@ -63310,7 +63382,7 @@
         <v>88514.60000000001</v>
       </c>
       <c r="C2063" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2063" t="inlineStr">
         <is>
@@ -63318,10 +63390,10 @@
         </is>
       </c>
       <c r="E2063" t="n">
-        <v>655.1079999999999</v>
+        <v>557.99</v>
       </c>
       <c r="F2063" t="n">
-        <v>18.5506</v>
+        <v>15.8005</v>
       </c>
     </row>
     <row r="2064">
@@ -63334,7 +63406,7 @@
         <v>84752.10000000001</v>
       </c>
       <c r="C2064" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2064" t="inlineStr">
         <is>
@@ -63342,10 +63414,10 @@
         </is>
       </c>
       <c r="E2064" t="n">
-        <v>627.2619999999999</v>
+        <v>534.272</v>
       </c>
       <c r="F2064" t="n">
-        <v>17.7621</v>
+        <v>15.1289</v>
       </c>
     </row>
     <row r="2065">
@@ -63358,7 +63430,7 @@
         <v>88054</v>
       </c>
       <c r="C2065" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2065" t="inlineStr">
         <is>
@@ -63366,10 +63438,10 @@
         </is>
       </c>
       <c r="E2065" t="n">
-        <v>651.7</v>
+        <v>555.087</v>
       </c>
       <c r="F2065" t="n">
-        <v>18.4541</v>
+        <v>15.7183</v>
       </c>
     </row>
     <row r="2066">
@@ -63382,7 +63454,7 @@
         <v>89403.3</v>
       </c>
       <c r="C2066" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2066" t="inlineStr">
         <is>
@@ -63390,10 +63462,10 @@
         </is>
       </c>
       <c r="E2066" t="n">
-        <v>661.686</v>
+        <v>563.593</v>
       </c>
       <c r="F2066" t="n">
-        <v>18.7369</v>
+        <v>15.9592</v>
       </c>
     </row>
     <row r="2067">
@@ -63406,7 +63478,7 @@
         <v>90169.7</v>
       </c>
       <c r="C2067" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2067" t="inlineStr">
         <is>
@@ -63414,10 +63486,10 @@
         </is>
       </c>
       <c r="E2067" t="n">
-        <v>667.3579999999999</v>
+        <v>568.424</v>
       </c>
       <c r="F2067" t="n">
-        <v>18.8975</v>
+        <v>16.096</v>
       </c>
     </row>
     <row r="2068">
@@ -63430,7 +63502,7 @@
         <v>89678.5</v>
       </c>
       <c r="C2068" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2068" t="inlineStr">
         <is>
@@ -63438,10 +63510,10 @@
         </is>
       </c>
       <c r="E2068" t="n">
-        <v>663.723</v>
+        <v>565.328</v>
       </c>
       <c r="F2068" t="n">
-        <v>18.7945</v>
+        <v>16.0083</v>
       </c>
     </row>
     <row r="2069">
@@ -63454,7 +63526,7 @@
         <v>84806.39999999999</v>
       </c>
       <c r="C2069" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2069" t="inlineStr">
         <is>
@@ -63462,10 +63534,10 @@
         </is>
       </c>
       <c r="E2069" t="n">
-        <v>627.664</v>
+        <v>534.614</v>
       </c>
       <c r="F2069" t="n">
-        <v>17.7735</v>
+        <v>15.1386</v>
       </c>
     </row>
     <row r="2070">
@@ -63478,7 +63550,7 @@
         <v>79621.3</v>
       </c>
       <c r="C2070" t="n">
-        <v>7882</v>
+        <v>6714</v>
       </c>
       <c r="D2070" t="inlineStr">
         <is>
@@ -63486,10 +63558,10 @@
         </is>
       </c>
       <c r="E2070" t="n">
-        <v>589.288</v>
+        <v>501.928</v>
       </c>
       <c r="F2070" t="n">
-        <v>16.6868</v>
+        <v>14.213</v>
       </c>
     </row>
     <row r="2071">
@@ -63502,18 +63574,18 @@
         <v>87666.89999999999</v>
       </c>
       <c r="C2071" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2071" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2071" t="n">
-        <v>614.748</v>
+        <v>607.052</v>
       </c>
       <c r="F2071" t="n">
-        <v>17.4077</v>
+        <v>17.1898</v>
       </c>
     </row>
     <row r="2072">
@@ -63526,18 +63598,18 @@
         <v>89746.10000000001</v>
       </c>
       <c r="C2072" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2072" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2072" t="n">
-        <v>629.328</v>
+        <v>621.449</v>
       </c>
       <c r="F2072" t="n">
-        <v>17.8206</v>
+        <v>17.5975</v>
       </c>
     </row>
     <row r="2073">
@@ -63550,18 +63622,18 @@
         <v>86872.8</v>
       </c>
       <c r="C2073" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2073" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2073" t="n">
-        <v>609.179</v>
+        <v>601.553</v>
       </c>
       <c r="F2073" t="n">
-        <v>17.25</v>
+        <v>17.0341</v>
       </c>
     </row>
     <row r="2074">
@@ -63574,18 +63646,18 @@
         <v>89082</v>
       </c>
       <c r="C2074" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2074" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2074" t="n">
-        <v>624.671</v>
+        <v>616.851</v>
       </c>
       <c r="F2074" t="n">
-        <v>17.6887</v>
+        <v>17.4673</v>
       </c>
     </row>
     <row r="2075">
@@ -63598,18 +63670,18 @@
         <v>89501</v>
       </c>
       <c r="C2075" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2075" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2075" t="n">
-        <v>627.609</v>
+        <v>619.752</v>
       </c>
       <c r="F2075" t="n">
-        <v>17.7719</v>
+        <v>17.5494</v>
       </c>
     </row>
     <row r="2076">
@@ -63622,18 +63694,18 @@
         <v>87527.10000000001</v>
       </c>
       <c r="C2076" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2076" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2076" t="n">
-        <v>613.768</v>
+        <v>606.0839999999999</v>
       </c>
       <c r="F2076" t="n">
-        <v>17.38</v>
+        <v>17.1624</v>
       </c>
     </row>
     <row r="2077">
@@ -63646,18 +63718,18 @@
         <v>88928.89999999999</v>
       </c>
       <c r="C2077" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2077" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2077" t="n">
-        <v>623.597</v>
+        <v>615.79</v>
       </c>
       <c r="F2077" t="n">
-        <v>17.6583</v>
+        <v>17.4372</v>
       </c>
     </row>
     <row r="2078">
@@ -63670,18 +63742,18 @@
         <v>89302.8</v>
       </c>
       <c r="C2078" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2078" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2078" t="n">
-        <v>626.2190000000001</v>
+        <v>618.379</v>
       </c>
       <c r="F2078" t="n">
-        <v>17.7325</v>
+        <v>17.5105</v>
       </c>
     </row>
     <row r="2079">
@@ -63694,18 +63766,18 @@
         <v>85396.89999999999</v>
       </c>
       <c r="C2079" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2079" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2079" t="n">
-        <v>598.83</v>
+        <v>591.333</v>
       </c>
       <c r="F2079" t="n">
-        <v>16.957</v>
+        <v>16.7447</v>
       </c>
     </row>
     <row r="2080">
@@ -63718,18 +63790,18 @@
         <v>85630.5</v>
       </c>
       <c r="C2080" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2080" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2080" t="n">
-        <v>600.468</v>
+        <v>592.951</v>
       </c>
       <c r="F2080" t="n">
-        <v>17.0034</v>
+        <v>16.7905</v>
       </c>
     </row>
     <row r="2081">
@@ -63742,18 +63814,18 @@
         <v>85778</v>
       </c>
       <c r="C2081" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2081" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2081" t="n">
-        <v>601.502</v>
+        <v>593.972</v>
       </c>
       <c r="F2081" t="n">
-        <v>17.0326</v>
+        <v>16.8194</v>
       </c>
     </row>
     <row r="2082">
@@ -63766,18 +63838,18 @@
         <v>82386.39999999999</v>
       </c>
       <c r="C2082" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2082" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2082" t="n">
-        <v>577.7190000000001</v>
+        <v>570.487</v>
       </c>
       <c r="F2082" t="n">
-        <v>16.3592</v>
+        <v>16.1544</v>
       </c>
     </row>
     <row r="2083">
@@ -63790,18 +63862,18 @@
         <v>68132.5</v>
       </c>
       <c r="C2083" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2083" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2083" t="n">
-        <v>477.767</v>
+        <v>471.785</v>
       </c>
       <c r="F2083" t="n">
-        <v>13.5289</v>
+        <v>13.3595</v>
       </c>
     </row>
     <row r="2084">
@@ -63814,18 +63886,18 @@
         <v>85655.39999999999</v>
       </c>
       <c r="C2084" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2084" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2084" t="n">
-        <v>600.643</v>
+        <v>593.123</v>
       </c>
       <c r="F2084" t="n">
-        <v>17.0083</v>
+        <v>16.7954</v>
       </c>
     </row>
     <row r="2085">
@@ -63838,18 +63910,18 @@
         <v>91446.5</v>
       </c>
       <c r="C2085" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2085" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2085" t="n">
-        <v>641.252</v>
+        <v>633.224</v>
       </c>
       <c r="F2085" t="n">
-        <v>18.1582</v>
+        <v>17.9309</v>
       </c>
     </row>
     <row r="2086">
@@ -63862,18 +63934,18 @@
         <v>89990.89999999999</v>
       </c>
       <c r="C2086" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2086" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2086" t="n">
-        <v>631.045</v>
+        <v>623.144</v>
       </c>
       <c r="F2086" t="n">
-        <v>17.8692</v>
+        <v>17.6455</v>
       </c>
     </row>
     <row r="2087">
@@ -63886,18 +63958,18 @@
         <v>89318.89999999999</v>
       </c>
       <c r="C2087" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2087" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2087" t="n">
-        <v>626.332</v>
+        <v>618.491</v>
       </c>
       <c r="F2087" t="n">
-        <v>17.7357</v>
+        <v>17.5137</v>
       </c>
     </row>
     <row r="2088">
@@ -63910,18 +63982,18 @@
         <v>90073.3</v>
       </c>
       <c r="C2088" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2088" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2088" t="n">
-        <v>631.622</v>
+        <v>623.715</v>
       </c>
       <c r="F2088" t="n">
-        <v>17.8855</v>
+        <v>17.6616</v>
       </c>
     </row>
     <row r="2089">
@@ -63934,18 +64006,18 @@
         <v>82859.10000000001</v>
       </c>
       <c r="C2089" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2089" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2089" t="n">
-        <v>581.034</v>
+        <v>573.76</v>
       </c>
       <c r="F2089" t="n">
-        <v>16.4531</v>
+        <v>16.2471</v>
       </c>
     </row>
     <row r="2090">
@@ -63958,18 +64030,18 @@
         <v>81030.39999999999</v>
       </c>
       <c r="C2090" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2090" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2090" t="n">
-        <v>568.211</v>
+        <v>561.097</v>
       </c>
       <c r="F2090" t="n">
-        <v>16.0899</v>
+        <v>15.8885</v>
       </c>
     </row>
     <row r="2091">
@@ -63982,18 +64054,18 @@
         <v>91415.7</v>
       </c>
       <c r="C2091" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2091" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2091" t="n">
-        <v>641.0359999999999</v>
+        <v>633.01</v>
       </c>
       <c r="F2091" t="n">
-        <v>18.1521</v>
+        <v>17.9248</v>
       </c>
     </row>
     <row r="2092">
@@ -64006,18 +64078,18 @@
         <v>91080.39999999999</v>
       </c>
       <c r="C2092" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2092" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2092" t="n">
-        <v>638.684</v>
+        <v>630.688</v>
       </c>
       <c r="F2092" t="n">
-        <v>18.0855</v>
+        <v>17.8591</v>
       </c>
     </row>
     <row r="2093">
@@ -64030,18 +64102,18 @@
         <v>91751.7</v>
       </c>
       <c r="C2093" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2093" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2093" t="n">
-        <v>643.3920000000001</v>
+        <v>635.337</v>
       </c>
       <c r="F2093" t="n">
-        <v>18.2188</v>
+        <v>17.9907</v>
       </c>
     </row>
     <row r="2094">
@@ -64054,18 +64126,18 @@
         <v>92237.5</v>
       </c>
       <c r="C2094" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2094" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2094" t="n">
-        <v>646.798</v>
+        <v>638.701</v>
       </c>
       <c r="F2094" t="n">
-        <v>18.3153</v>
+        <v>18.086</v>
       </c>
     </row>
     <row r="2095">
@@ -64078,18 +64150,18 @@
         <v>92785.2</v>
       </c>
       <c r="C2095" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2095" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2095" t="n">
-        <v>650.639</v>
+        <v>642.4930000000001</v>
       </c>
       <c r="F2095" t="n">
-        <v>18.424</v>
+        <v>18.1934</v>
       </c>
     </row>
     <row r="2096">
@@ -64102,18 +64174,18 @@
         <v>90940.5</v>
       </c>
       <c r="C2096" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2096" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2096" t="n">
-        <v>637.703</v>
+        <v>629.72</v>
       </c>
       <c r="F2096" t="n">
-        <v>18.0577</v>
+        <v>17.8317</v>
       </c>
     </row>
     <row r="2097">
@@ -64126,18 +64198,18 @@
         <v>86490.8</v>
       </c>
       <c r="C2097" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2097" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2097" t="n">
-        <v>606.501</v>
+        <v>598.908</v>
       </c>
       <c r="F2097" t="n">
-        <v>17.1742</v>
+        <v>16.9592</v>
       </c>
     </row>
     <row r="2098">
@@ -64150,18 +64222,18 @@
         <v>90882.8</v>
       </c>
       <c r="C2098" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2098" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2098" t="n">
-        <v>637.299</v>
+        <v>629.3200000000001</v>
       </c>
       <c r="F2098" t="n">
-        <v>18.0463</v>
+        <v>17.8204</v>
       </c>
     </row>
     <row r="2099">
@@ -64174,18 +64246,18 @@
         <v>91623.3</v>
       </c>
       <c r="C2099" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2099" t="inlineStr">
         <is>
-          <t>trailing 12-month mean</t>
+          <t>monthly MINEM</t>
         </is>
       </c>
       <c r="E2099" t="n">
-        <v>642.491</v>
+        <v>634.448</v>
       </c>
       <c r="F2099" t="n">
-        <v>18.1933</v>
+        <v>17.9656</v>
       </c>
     </row>
     <row r="2100">
@@ -64195,21 +64267,45 @@
         </is>
       </c>
       <c r="B2100" t="n">
-        <v>88516.39999999999</v>
+        <v>89079.5</v>
       </c>
       <c r="C2100" t="n">
-        <v>7468</v>
+        <v>7375</v>
       </c>
       <c r="D2100" t="inlineStr">
         <is>
+          <t>monthly MINEM</t>
+        </is>
+      </c>
+      <c r="E2100" t="n">
+        <v>616.833</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>17.4668</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2101" t="n">
+        <v>92153.39999999999</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>7383</v>
+      </c>
+      <c r="D2101" t="inlineStr">
+        <is>
           <t>trailing 12-month mean</t>
         </is>
       </c>
-      <c r="E2100" t="n">
-        <v>620.705</v>
-      </c>
-      <c r="F2100" t="n">
-        <v>17.5764</v>
+      <c r="E2101" t="n">
+        <v>638.809</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>18.0891</v>
       </c>
     </row>
   </sheetData>
@@ -64223,7 +64319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG69"/>
+  <dimension ref="A1:AG70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70842,25 +70938,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>8.4659</v>
+        <v>7.7868</v>
       </c>
       <c r="C69" t="n">
-        <v>148.4791</v>
+        <v>149.4146</v>
       </c>
       <c r="D69" t="n">
-        <v>616.9935</v>
+        <v>523.7268</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8265</v>
+        <v>0.7855</v>
       </c>
       <c r="F69" t="n">
-        <v>29.5481</v>
+        <v>27.6694</v>
       </c>
       <c r="G69" t="n">
-        <v>894.8108999999999</v>
+        <v>794.0571</v>
       </c>
       <c r="H69" t="n">
-        <v>90.49769999999999</v>
+        <v>84.6741</v>
       </c>
       <c r="I69" t="n">
         <v>0.3805</v>
@@ -70936,6 +71032,109 @@
       </c>
       <c r="AG69" t="n">
         <v>0.1414</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>8.851000000000001</v>
+      </c>
+      <c r="C70" t="n">
+        <v>169.8346</v>
+      </c>
+      <c r="D70" t="n">
+        <v>595.3028</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.8928</v>
+      </c>
+      <c r="F70" t="n">
+        <v>31.4508</v>
+      </c>
+      <c r="G70" t="n">
+        <v>902.5782</v>
+      </c>
+      <c r="H70" t="n">
+        <v>96.2462</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="J70" t="n">
+        <v>13.1773</v>
+      </c>
+      <c r="K70" t="n">
+        <v>12.8071</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.0463</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.3685</v>
+      </c>
+      <c r="N70" t="n">
+        <v>30.6692</v>
+      </c>
+      <c r="O70" t="n">
+        <v>2.8941</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.2768</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>3.5111</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3.4133</v>
+      </c>
+      <c r="U70" t="n">
+        <v>10.0066</v>
+      </c>
+      <c r="V70" t="n">
+        <v>2.7714</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.2403</v>
+      </c>
+      <c r="X70" t="n">
+        <v>3.0586</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.1882</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>3.4872</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>28.122</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1.2294</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>29.5299</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0.152</v>
       </c>
     </row>
   </sheetData>
